--- a/output/yearly_total_coral_cover_iteration_22_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_22_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.256358672359809</v>
+        <v>1.255799076168389</v>
       </c>
       <c r="C3" t="n">
-        <v>4.595037623113117</v>
+        <v>4.64691317180552</v>
       </c>
       <c r="D3" t="n">
-        <v>6.050751723395273</v>
+        <v>6.183444743101273</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9021480188682</v>
+        <v>12.08615699107518</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.38071501683775</v>
+        <v>1.377532037366537</v>
       </c>
       <c r="C4" t="n">
-        <v>5.02836241805757</v>
+        <v>5.180417124818</v>
       </c>
       <c r="D4" t="n">
-        <v>6.287403907967612</v>
+        <v>6.477859248551424</v>
       </c>
       <c r="E4" t="n">
-        <v>12.69648134286293</v>
+        <v>13.03580841073596</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.544091607075133</v>
+        <v>1.542606587386775</v>
       </c>
       <c r="C5" t="n">
-        <v>5.540129010836667</v>
+        <v>5.914614159597813</v>
       </c>
       <c r="D5" t="n">
-        <v>6.572409998811286</v>
+        <v>6.887068378785015</v>
       </c>
       <c r="E5" t="n">
-        <v>13.65663061672308</v>
+        <v>14.3442891257696</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.736295373750609</v>
+        <v>1.739654371677368</v>
       </c>
       <c r="C6" t="n">
-        <v>6.142877129964444</v>
+        <v>6.809242142230674</v>
       </c>
       <c r="D6" t="n">
-        <v>6.934852530987486</v>
+        <v>7.300631172260076</v>
       </c>
       <c r="E6" t="n">
-        <v>14.81402503470254</v>
+        <v>15.84952768616812</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.964509784899252</v>
+        <v>1.960700569656208</v>
       </c>
       <c r="C7" t="n">
-        <v>6.844216404175445</v>
+        <v>7.845175285705853</v>
       </c>
       <c r="D7" t="n">
-        <v>7.322187410051253</v>
+        <v>7.700708957268354</v>
       </c>
       <c r="E7" t="n">
-        <v>16.13091359912595</v>
+        <v>17.50658481263041</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.204166037278528</v>
+        <v>1.184872903455598</v>
       </c>
       <c r="C8" t="n">
-        <v>4.425701774388132</v>
+        <v>5.490994943138968</v>
       </c>
       <c r="D8" t="n">
-        <v>5.673120009259528</v>
+        <v>5.874665133542371</v>
       </c>
       <c r="E8" t="n">
-        <v>11.30298782092619</v>
+        <v>12.55053298013694</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.524660813612828</v>
+        <v>1.467311834889042</v>
       </c>
       <c r="C9" t="n">
-        <v>5.265606748821875</v>
+        <v>6.738432719987881</v>
       </c>
       <c r="D9" t="n">
-        <v>6.296566192768159</v>
+        <v>6.405423864034458</v>
       </c>
       <c r="E9" t="n">
-        <v>13.08683375520286</v>
+        <v>14.61116841891138</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.874162357054215</v>
+        <v>1.761360462692199</v>
       </c>
       <c r="C10" t="n">
-        <v>6.214649180069185</v>
+        <v>8.114926877736401</v>
       </c>
       <c r="D10" t="n">
-        <v>6.968745718702188</v>
+        <v>6.955390321913609</v>
       </c>
       <c r="E10" t="n">
-        <v>15.05755725582559</v>
+        <v>16.83167766234221</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.251809844969864</v>
+        <v>2.054253652020679</v>
       </c>
       <c r="C11" t="n">
-        <v>7.294658779174759</v>
+        <v>9.588359464326313</v>
       </c>
       <c r="D11" t="n">
-        <v>7.655698303100576</v>
+        <v>7.522873071509645</v>
       </c>
       <c r="E11" t="n">
-        <v>17.2021669272452</v>
+        <v>19.16548618785664</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.643491472232569</v>
+        <v>2.347633264517615</v>
       </c>
       <c r="C12" t="n">
-        <v>8.450583382749183</v>
+        <v>11.13348769361977</v>
       </c>
       <c r="D12" t="n">
-        <v>8.295979548348019</v>
+        <v>7.975784183365715</v>
       </c>
       <c r="E12" t="n">
-        <v>19.39005440332977</v>
+        <v>21.4569051415031</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.043314405938177</v>
+        <v>2.640856052550128</v>
       </c>
       <c r="C13" t="n">
-        <v>9.656085044061946</v>
+        <v>12.69497264509636</v>
       </c>
       <c r="D13" t="n">
-        <v>8.959511842556703</v>
+        <v>8.458919703766558</v>
       </c>
       <c r="E13" t="n">
-        <v>21.65891129255683</v>
+        <v>23.79474840141304</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.759615862752686</v>
+        <v>1.53123189431375</v>
       </c>
       <c r="C14" t="n">
-        <v>6.902236139569455</v>
+        <v>8.917754358911115</v>
       </c>
       <c r="D14" t="n">
-        <v>6.874786473758715</v>
+        <v>6.385277250944212</v>
       </c>
       <c r="E14" t="n">
-        <v>15.53663847608086</v>
+        <v>16.83426350416908</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.844055982794954</v>
+        <v>1.566025032952257</v>
       </c>
       <c r="C15" t="n">
-        <v>7.308316442477063</v>
+        <v>9.550304222234375</v>
       </c>
       <c r="D15" t="n">
-        <v>7.019604077612162</v>
+        <v>6.400847769533567</v>
       </c>
       <c r="E15" t="n">
-        <v>16.17197650288418</v>
+        <v>17.5171770247202</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.183848680711818</v>
+        <v>1.813199652450476</v>
       </c>
       <c r="C16" t="n">
-        <v>8.560005495483578</v>
+        <v>11.19684238441191</v>
       </c>
       <c r="D16" t="n">
-        <v>7.614611908725026</v>
+        <v>6.861032188422217</v>
       </c>
       <c r="E16" t="n">
-        <v>18.35846608492042</v>
+        <v>19.87107422528461</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.790963066949286</v>
+        <v>1.457394649477348</v>
       </c>
       <c r="C17" t="n">
-        <v>7.892358151733491</v>
+        <v>10.21115787187108</v>
       </c>
       <c r="D17" t="n">
-        <v>7.173630474931444</v>
+        <v>6.359005682378568</v>
       </c>
       <c r="E17" t="n">
-        <v>16.85695169361422</v>
+        <v>18.02755820372699</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.085624822901924</v>
+        <v>1.664455057780043</v>
       </c>
       <c r="C18" t="n">
-        <v>9.178133485031454</v>
+        <v>11.88026641376925</v>
       </c>
       <c r="D18" t="n">
-        <v>7.715182143548068</v>
+        <v>6.752077828204905</v>
       </c>
       <c r="E18" t="n">
-        <v>18.97894045148145</v>
+        <v>20.2967992997542</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.133013784585918</v>
+        <v>1.667606467910675</v>
       </c>
       <c r="C19" t="n">
-        <v>9.815621539307079</v>
+        <v>12.68656598579011</v>
       </c>
       <c r="D19" t="n">
-        <v>7.901498222860029</v>
+        <v>6.841446321722493</v>
       </c>
       <c r="E19" t="n">
-        <v>19.85013354675302</v>
+        <v>21.19561877542328</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.414451398962351</v>
+        <v>1.854374151166588</v>
       </c>
       <c r="C20" t="n">
-        <v>11.31316966988812</v>
+        <v>14.5574924032503</v>
       </c>
       <c r="D20" t="n">
-        <v>8.446859072569133</v>
+        <v>7.253328753562199</v>
       </c>
       <c r="E20" t="n">
-        <v>22.1744801414196</v>
+        <v>23.66519530797909</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.45891635841893</v>
+        <v>1.100018850177424</v>
       </c>
       <c r="C21" t="n">
-        <v>8.411427797922865</v>
+        <v>10.70873706081449</v>
       </c>
       <c r="D21" t="n">
-        <v>7.099665602893489</v>
+        <v>6.033850842732025</v>
       </c>
       <c r="E21" t="n">
-        <v>16.97000975923529</v>
+        <v>17.84260675372393</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_22_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_22_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.255799076168389</v>
+        <v>1.274521004888375</v>
       </c>
       <c r="C3" t="n">
-        <v>4.64691317180552</v>
+        <v>4.587321086157737</v>
       </c>
       <c r="D3" t="n">
-        <v>6.183444743101273</v>
+        <v>6.074205676049729</v>
       </c>
       <c r="E3" t="n">
-        <v>12.08615699107518</v>
+        <v>11.93604776709584</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.377532037366537</v>
+        <v>1.431612800571315</v>
       </c>
       <c r="C4" t="n">
-        <v>5.180417124818</v>
+        <v>5.041752362638434</v>
       </c>
       <c r="D4" t="n">
-        <v>6.477859248551424</v>
+        <v>6.296720007241898</v>
       </c>
       <c r="E4" t="n">
-        <v>13.03580841073596</v>
+        <v>12.77008517045165</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.542606587386775</v>
+        <v>1.637209240920267</v>
       </c>
       <c r="C5" t="n">
-        <v>5.914614159597813</v>
+        <v>5.627928638235301</v>
       </c>
       <c r="D5" t="n">
-        <v>6.887068378785015</v>
+        <v>6.546674018671025</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3442891257696</v>
+        <v>13.81181189782659</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.739654371677368</v>
+        <v>1.872616685259494</v>
       </c>
       <c r="C6" t="n">
-        <v>6.809242142230674</v>
+        <v>6.382353925466725</v>
       </c>
       <c r="D6" t="n">
-        <v>7.300631172260076</v>
+        <v>6.874498338458066</v>
       </c>
       <c r="E6" t="n">
-        <v>15.84952768616812</v>
+        <v>15.12946894918428</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.960700569656208</v>
+        <v>2.149094004803192</v>
       </c>
       <c r="C7" t="n">
-        <v>7.845175285705853</v>
+        <v>7.26947089992512</v>
       </c>
       <c r="D7" t="n">
-        <v>7.700708957268354</v>
+        <v>7.193090276928751</v>
       </c>
       <c r="E7" t="n">
-        <v>17.50658481263041</v>
+        <v>16.61165518165706</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.184872903455598</v>
+        <v>1.377664840667179</v>
       </c>
       <c r="C8" t="n">
-        <v>5.490994943138968</v>
+        <v>4.992201958374507</v>
       </c>
       <c r="D8" t="n">
-        <v>5.874665133542371</v>
+        <v>5.344132252279256</v>
       </c>
       <c r="E8" t="n">
-        <v>12.55053298013694</v>
+        <v>11.71399905132094</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.467311834889042</v>
+        <v>1.768088356202164</v>
       </c>
       <c r="C9" t="n">
-        <v>6.738432719987881</v>
+        <v>6.182345204737077</v>
       </c>
       <c r="D9" t="n">
-        <v>6.405423864034458</v>
+        <v>5.838138220122391</v>
       </c>
       <c r="E9" t="n">
-        <v>14.61116841891138</v>
+        <v>13.78857178106163</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.761360462692199</v>
+        <v>2.179473401380019</v>
       </c>
       <c r="C10" t="n">
-        <v>8.114926877736401</v>
+        <v>7.567319979338427</v>
       </c>
       <c r="D10" t="n">
-        <v>6.955390321913609</v>
+        <v>6.239785556603977</v>
       </c>
       <c r="E10" t="n">
-        <v>16.83167766234221</v>
+        <v>15.98657893732242</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.054253652020679</v>
+        <v>2.606784333348092</v>
       </c>
       <c r="C11" t="n">
-        <v>9.588359464326313</v>
+        <v>9.086828875445949</v>
       </c>
       <c r="D11" t="n">
-        <v>7.522873071509645</v>
+        <v>6.678849078482357</v>
       </c>
       <c r="E11" t="n">
-        <v>19.16548618785664</v>
+        <v>18.3724622872764</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.347633264517615</v>
+        <v>3.042301015403991</v>
       </c>
       <c r="C12" t="n">
-        <v>11.13348769361977</v>
+        <v>10.7223169169778</v>
       </c>
       <c r="D12" t="n">
-        <v>7.975784183365715</v>
+        <v>7.160519685749117</v>
       </c>
       <c r="E12" t="n">
-        <v>21.4569051415031</v>
+        <v>20.92513761813091</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.640856052550128</v>
+        <v>3.458995364638949</v>
       </c>
       <c r="C13" t="n">
-        <v>12.69497264509636</v>
+        <v>12.39520485068152</v>
       </c>
       <c r="D13" t="n">
-        <v>8.458919703766558</v>
+        <v>7.612771280657014</v>
       </c>
       <c r="E13" t="n">
-        <v>23.79474840141304</v>
+        <v>23.46697149597749</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.53123189431375</v>
+        <v>1.982158432351353</v>
       </c>
       <c r="C14" t="n">
-        <v>8.917754358911115</v>
+        <v>8.668311902216086</v>
       </c>
       <c r="D14" t="n">
-        <v>6.385277250944212</v>
+        <v>5.800793755220874</v>
       </c>
       <c r="E14" t="n">
-        <v>16.83426350416908</v>
+        <v>16.45126408978831</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.566025032952257</v>
+        <v>2.056712353011855</v>
       </c>
       <c r="C15" t="n">
-        <v>9.550304222234375</v>
+        <v>9.461004451056088</v>
       </c>
       <c r="D15" t="n">
-        <v>6.400847769533567</v>
+        <v>5.788924425476529</v>
       </c>
       <c r="E15" t="n">
-        <v>17.5171770247202</v>
+        <v>17.30664122954447</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.813199652450476</v>
+        <v>2.421834141698287</v>
       </c>
       <c r="C16" t="n">
-        <v>11.19684238441191</v>
+        <v>11.22678568939144</v>
       </c>
       <c r="D16" t="n">
-        <v>6.861032188422217</v>
+        <v>6.182811421897393</v>
       </c>
       <c r="E16" t="n">
-        <v>19.87107422528461</v>
+        <v>19.83143125298712</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.457394649477348</v>
+        <v>1.969032465545573</v>
       </c>
       <c r="C17" t="n">
-        <v>10.21115787187108</v>
+        <v>10.40690854662085</v>
       </c>
       <c r="D17" t="n">
-        <v>6.359005682378568</v>
+        <v>5.703355295574378</v>
       </c>
       <c r="E17" t="n">
-        <v>18.02755820372699</v>
+        <v>18.0792963077408</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.664455057780043</v>
+        <v>2.265039215853029</v>
       </c>
       <c r="C18" t="n">
-        <v>11.88026641376925</v>
+        <v>12.17677385540587</v>
       </c>
       <c r="D18" t="n">
-        <v>6.752077828204905</v>
+        <v>6.131161675176968</v>
       </c>
       <c r="E18" t="n">
-        <v>20.2967992997542</v>
+        <v>20.57297474643587</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.667606467910675</v>
+        <v>2.28692237218069</v>
       </c>
       <c r="C19" t="n">
-        <v>12.68656598579011</v>
+        <v>13.03671612198678</v>
       </c>
       <c r="D19" t="n">
-        <v>6.841446321722493</v>
+        <v>6.215248366045707</v>
       </c>
       <c r="E19" t="n">
-        <v>21.19561877542328</v>
+        <v>21.53888686021318</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.854374151166588</v>
+        <v>2.562008078910647</v>
       </c>
       <c r="C20" t="n">
-        <v>14.5574924032503</v>
+        <v>15.07178093811999</v>
       </c>
       <c r="D20" t="n">
-        <v>7.253328753562199</v>
+        <v>6.633345260853296</v>
       </c>
       <c r="E20" t="n">
-        <v>23.66519530797909</v>
+        <v>24.26713427788393</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.100018850177424</v>
+        <v>1.528394643448477</v>
       </c>
       <c r="C21" t="n">
-        <v>10.70873706081449</v>
+        <v>11.1153278725283</v>
       </c>
       <c r="D21" t="n">
-        <v>6.033850842732025</v>
+        <v>5.53725340149286</v>
       </c>
       <c r="E21" t="n">
-        <v>17.84260675372393</v>
+        <v>18.18097591746964</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_22_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_22_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.274521004888375</v>
+        <v>2.605440119230055</v>
       </c>
       <c r="C3" t="n">
-        <v>4.587321086157737</v>
+        <v>7.688623037504699</v>
       </c>
       <c r="D3" t="n">
-        <v>6.074205676049729</v>
+        <v>8.155857040610757</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93604776709584</v>
+        <v>18.44992019734551</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.431612800571315</v>
+        <v>1.106003067877654</v>
       </c>
       <c r="C4" t="n">
-        <v>5.041752362638434</v>
+        <v>4.424450331239368</v>
       </c>
       <c r="D4" t="n">
-        <v>6.296720007241898</v>
+        <v>5.811495163475922</v>
       </c>
       <c r="E4" t="n">
-        <v>12.77008517045165</v>
+        <v>11.34194856259294</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.637209240920267</v>
+        <v>1.225153920461356</v>
       </c>
       <c r="C5" t="n">
-        <v>5.627928638235301</v>
+        <v>4.968451957020576</v>
       </c>
       <c r="D5" t="n">
-        <v>6.546674018671025</v>
+        <v>6.194850713644781</v>
       </c>
       <c r="E5" t="n">
-        <v>13.81181189782659</v>
+        <v>12.38845659112671</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.872616685259494</v>
+        <v>1.354073648864021</v>
       </c>
       <c r="C6" t="n">
-        <v>6.382353925466725</v>
+        <v>5.63661815132298</v>
       </c>
       <c r="D6" t="n">
-        <v>6.874498338458066</v>
+        <v>6.571519387141954</v>
       </c>
       <c r="E6" t="n">
-        <v>15.12946894918428</v>
+        <v>13.56221118732896</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.149094004803192</v>
+        <v>1.485907520899829</v>
       </c>
       <c r="C7" t="n">
-        <v>7.26947089992512</v>
+        <v>6.443387759491165</v>
       </c>
       <c r="D7" t="n">
-        <v>7.193090276928751</v>
+        <v>7.119443266375862</v>
       </c>
       <c r="E7" t="n">
-        <v>16.61165518165706</v>
+        <v>15.04873854676686</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.377664840667179</v>
+        <v>1.642076472050844</v>
       </c>
       <c r="C8" t="n">
-        <v>4.992201958374507</v>
+        <v>7.367020677101583</v>
       </c>
       <c r="D8" t="n">
-        <v>5.344132252279256</v>
+        <v>7.597844973418398</v>
       </c>
       <c r="E8" t="n">
-        <v>11.71399905132094</v>
+        <v>16.60694212257082</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.768088356202164</v>
+        <v>1.800408040353929</v>
       </c>
       <c r="C9" t="n">
-        <v>6.182345204737077</v>
+        <v>8.409032931080691</v>
       </c>
       <c r="D9" t="n">
-        <v>5.838138220122391</v>
+        <v>8.129646731989885</v>
       </c>
       <c r="E9" t="n">
-        <v>13.78857178106163</v>
+        <v>18.3390877034245</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.179473401380019</v>
+        <v>1.126005711908837</v>
       </c>
       <c r="C10" t="n">
-        <v>7.567319979338427</v>
+        <v>6.308121698867455</v>
       </c>
       <c r="D10" t="n">
-        <v>6.239785556603977</v>
+        <v>6.439420636833423</v>
       </c>
       <c r="E10" t="n">
-        <v>15.98657893732242</v>
+        <v>13.87354804760971</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.606784333348092</v>
+        <v>1.07422833798686</v>
       </c>
       <c r="C11" t="n">
-        <v>9.086828875445949</v>
+        <v>6.566232987790985</v>
       </c>
       <c r="D11" t="n">
-        <v>6.678849078482357</v>
+        <v>6.388055596947232</v>
       </c>
       <c r="E11" t="n">
-        <v>18.3724622872764</v>
+        <v>14.02851692272508</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.042301015403991</v>
+        <v>1.178283777159979</v>
       </c>
       <c r="C12" t="n">
-        <v>10.7223169169778</v>
+        <v>7.685857339622217</v>
       </c>
       <c r="D12" t="n">
-        <v>7.160519685749117</v>
+        <v>6.919338184577435</v>
       </c>
       <c r="E12" t="n">
-        <v>20.92513761813091</v>
+        <v>15.78347930135963</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.458995364638949</v>
+        <v>0.9408873647960582</v>
       </c>
       <c r="C13" t="n">
-        <v>12.39520485068152</v>
+        <v>7.286119126884044</v>
       </c>
       <c r="D13" t="n">
-        <v>7.612771280657014</v>
+        <v>6.43220479120721</v>
       </c>
       <c r="E13" t="n">
-        <v>23.46697149597749</v>
+        <v>14.65921128288731</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.982158432351353</v>
+        <v>1.034045404452038</v>
       </c>
       <c r="C14" t="n">
-        <v>8.668311902216086</v>
+        <v>8.507128564132843</v>
       </c>
       <c r="D14" t="n">
-        <v>5.800793755220874</v>
+        <v>6.974021531703981</v>
       </c>
       <c r="E14" t="n">
-        <v>16.45126408978831</v>
+        <v>16.51519550028886</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.056712353011855</v>
+        <v>1.010228205147011</v>
       </c>
       <c r="C15" t="n">
-        <v>9.461004451056088</v>
+        <v>9.172105554127377</v>
       </c>
       <c r="D15" t="n">
-        <v>5.788924425476529</v>
+        <v>7.140280505418179</v>
       </c>
       <c r="E15" t="n">
-        <v>17.30664122954447</v>
+        <v>17.32261426469257</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.421834141698287</v>
+        <v>1.108452062956904</v>
       </c>
       <c r="C16" t="n">
-        <v>11.22678568939144</v>
+        <v>10.8011391547382</v>
       </c>
       <c r="D16" t="n">
-        <v>6.182811421897393</v>
+        <v>7.696008610884129</v>
       </c>
       <c r="E16" t="n">
-        <v>19.83143125298712</v>
+        <v>19.60559982857923</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.969032465545573</v>
+        <v>0.6642504966933919</v>
       </c>
       <c r="C17" t="n">
-        <v>10.40690854662085</v>
+        <v>8.26116149431085</v>
       </c>
       <c r="D17" t="n">
-        <v>5.703355295574378</v>
+        <v>6.494211976207438</v>
       </c>
       <c r="E17" t="n">
-        <v>18.0792963077408</v>
+        <v>15.41962396721168</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.265039215853029</v>
+        <v>0.5197175996741765</v>
       </c>
       <c r="C18" t="n">
-        <v>12.17677385540587</v>
+        <v>7.442629345895069</v>
       </c>
       <c r="D18" t="n">
-        <v>6.131161675176968</v>
+        <v>6.045111488899735</v>
       </c>
       <c r="E18" t="n">
-        <v>20.57297474643587</v>
+        <v>14.00745843446898</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.28692237218069</v>
+        <v>0.6036570283872787</v>
       </c>
       <c r="C19" t="n">
-        <v>13.03671612198678</v>
+        <v>9.30736093534146</v>
       </c>
       <c r="D19" t="n">
-        <v>6.215248366045707</v>
+        <v>6.694714309845764</v>
       </c>
       <c r="E19" t="n">
-        <v>21.53888686021318</v>
+        <v>16.6057322735745</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.562008078910647</v>
+        <v>0.6817256058289851</v>
       </c>
       <c r="C20" t="n">
-        <v>15.07178093811999</v>
+        <v>11.35069206714443</v>
       </c>
       <c r="D20" t="n">
-        <v>6.633345260853296</v>
+        <v>7.303260441800193</v>
       </c>
       <c r="E20" t="n">
-        <v>24.26713427788393</v>
+        <v>19.33567811477361</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.528394643448477</v>
+        <v>0.7558868274077892</v>
       </c>
       <c r="C21" t="n">
-        <v>11.1153278725283</v>
+        <v>13.54720529324103</v>
       </c>
       <c r="D21" t="n">
-        <v>5.53725340149286</v>
+        <v>7.913730799254945</v>
       </c>
       <c r="E21" t="n">
-        <v>18.18097591746964</v>
+        <v>22.21682291990377</v>
       </c>
     </row>
   </sheetData>
